--- a/data/trans_bre/CAGE_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/CAGE_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE)</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,7</t>
+          <t>-2,0; 0,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,24; -0,59</t>
+          <t>-4,16; -0,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,73</t>
+          <t>-2,21; 0,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 13,04</t>
+          <t>0,09; 12,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 198,08</t>
+          <t>-100,0; 178,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-92,06; -11,03</t>
+          <t>-93,34; -17,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 207,01</t>
+          <t>-100,0; 154,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,45</t>
+          <t>-1,26; 0,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,47; -1,18</t>
+          <t>-3,34; -1,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,19; -0,22</t>
+          <t>-3,07; -0,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 0,04</t>
+          <t>-7,14; 0,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 291,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-92,63; -1,66</t>
+          <t>-89,56; 3,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,54; -0,02</t>
+          <t>-1,6; -0,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; -1,09</t>
+          <t>-3,43; -1,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; -0,08</t>
+          <t>-1,94; -0,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,05</t>
+          <t>-1,95; 2,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 38,26</t>
+          <t>-100,0; -1,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 533,78</t>
+          <t>-100,0; 669,91</t>
         </is>
       </c>
     </row>
@@ -965,17 +965,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,78; -1,0</t>
+          <t>-4,0; -1,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; -0,04</t>
+          <t>-2,35; 0,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,25</t>
+          <t>-2,51; 1,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 22,25</t>
+          <t>-100,0; 49,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-93,23; 223,46</t>
+          <t>-95,19; 188,47</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,44; -0,44</t>
+          <t>-3,57; -0,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,15</t>
+          <t>-2,81; 0,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 0,03</t>
+          <t>-2,97; 0,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 1,63</t>
+          <t>-4,97; 1,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 90,39</t>
+          <t>-100,0; 23,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 87,6</t>
+          <t>-100,0; 70,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-78,01; 90,97</t>
+          <t>-81,19; 61,35</t>
         </is>
       </c>
     </row>
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,57; -0,63</t>
+          <t>-4,03; -0,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,58</t>
+          <t>-0,87; 0,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,29; -0,56</t>
+          <t>-4,13; -0,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -26,5</t>
+          <t>-100,0; -10,29</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,0</t>
+          <t>-2,87; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,0</t>
+          <t>-4,58; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,0</t>
+          <t>-1,77; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 4,15</t>
+          <t>-3,82; 4,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,92; -0,18</t>
+          <t>-0,86; -0,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,32; -1,31</t>
+          <t>-2,29; -1,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,47; -0,5</t>
+          <t>-1,47; -0,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,27</t>
+          <t>-2,08; 0,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-86,85; -26,54</t>
+          <t>-86,05; -20,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-97,25; -81,54</t>
+          <t>-97,73; -82,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-81,91; -38,73</t>
+          <t>-82,48; -38,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-75,12; 14,99</t>
+          <t>-76,01; 12,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/CAGE_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/CAGE_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,94</t>
+          <t>4,57</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4066,55%</t>
+          <t>459,71%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,79</t>
+          <t>-1,89; 0,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,16; -0,59</t>
+          <t>-4,16; -0,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 0,58</t>
+          <t>-2,06; 0,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 12,21</t>
+          <t>0,0; 13,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 178,63</t>
+          <t>-100,0; 294,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-93,34; -17,26</t>
+          <t>-92,67; -15,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 154,16</t>
+          <t>-100,0; 257,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,56</t>
+          <t>-2,64</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-80,79%</t>
+          <t>-82,27%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,56</t>
+          <t>-1,34; 0,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,34; -1,16</t>
+          <t>-3,29; -1,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,07; -0,13</t>
+          <t>-3,12; -0,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 0,04</t>
+          <t>-6,37; -0,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 219,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-89,56; 3,64</t>
+          <t>-89,49; 12,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-0,6</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>-32,85%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; -0,02</t>
+          <t>-1,47; -0,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,43; -1,13</t>
+          <t>-3,23; -1,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,94; -0,19</t>
+          <t>-1,96; -0,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,08</t>
+          <t>-2,61; 1,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -1,97</t>
+          <t>-100,0; 21,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 669,91</t>
+          <t>-100,0; 419,6</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,65</t>
+          <t>-0,62</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-36,06%</t>
+          <t>-31,3%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,14</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,0; -1,02</t>
+          <t>-3,87; -1,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 0,02</t>
+          <t>-2,51; 0,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 1,2</t>
+          <t>-2,61; 1,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 49,25</t>
+          <t>-93,61; 46,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-95,19; 188,47</t>
+          <t>-87,35; 155,44</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,83</t>
+          <t>-1,58</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-41,0%</t>
+          <t>-37,93%</t>
         </is>
       </c>
     </row>
@@ -1060,27 +1060,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,57; -0,46</t>
+          <t>-3,64; -0,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,07</t>
+          <t>-2,4; 0,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 0,23</t>
+          <t>-3,15; 0,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 1,44</t>
+          <t>-4,36; 1,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 23,64</t>
+          <t>-100,0; 10,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 70,1</t>
+          <t>-100,0; 63,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-81,19; 61,35</t>
+          <t>-77,76; 77,19</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-1,95</t>
+          <t>-1,78</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-92,35%</t>
+          <t>-75,41%</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-4,03; -0,34</t>
+          <t>-4,48; -0,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,43</t>
+          <t>-3,94; 0,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -10,29</t>
+          <t>-100,0; 98,08</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-0,8</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-36,22%</t>
+          <t>-35,83%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 0,0</t>
+          <t>-2,41; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 0,0</t>
+          <t>-4,12; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,0</t>
+          <t>-2,12; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 4,84</t>
+          <t>-3,74; 4,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,93</t>
+          <t>-0,61</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-41,49%</t>
+          <t>-24,59%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,86; -0,18</t>
+          <t>-0,88; -0,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-2,29; -1,28</t>
+          <t>-2,36; -1,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,47; -0,48</t>
+          <t>-1,46; -0,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,22</t>
+          <t>-1,75; 0,66</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-86,05; -20,23</t>
+          <t>-84,41; -11,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-97,73; -82,0</t>
+          <t>-97,5; -80,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-82,48; -38,48</t>
+          <t>-82,98; -41,07</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-76,01; 12,45</t>
+          <t>-61,41; 41,76</t>
         </is>
       </c>
     </row>
